--- a/tests/build_food_db/fixtures/afcd_nutrients_slice.xlsx
+++ b/tests/build_food_db/fixtures/afcd_nutrients_slice.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nutrients per 100g" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All solids &amp; liquids per 100 g" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,296 +414,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Public Food Key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Food Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Energy with dietary fibre, equated 
-(kJ)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Protein 
-(g)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Total fat 
-(g)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Available carbohydrate, with sugar alcohols 
-(g)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Total dietary fibre 
-(g)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Total sugars 
-(g)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Sodium (Na) 
-(mg)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Calcium (Ca) 
-(mg)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Iron (Fe) 
-(mg)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Vitamin C 
-(mg)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Vitamin D3 equivalents 
-(µg)</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Vitamin B12 
-(µg)</t>
+          <t>placeholder cover sheet</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>F001234</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Broccoli, fresh, raw</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Release 3 - Nutrient profiles (per 100 g)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F001235</t>
+          <t>Public Food Key</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrot, mature, fresh, raw</t>
+          <t>Food Name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>Energy with dietary fibre, equated 
+(kJ)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>Protein 
+(g)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>Total fat 
+(g)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>Available carbohydrate, with sugar alcohols 
+(g)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Total dietary fibre 
+(g)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>Total sugars 
+(g)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Sodium (Na) 
+(mg)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Calcium (Ca) 
+(mg)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>Iron (Fe) 
+(mg)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Vitamin C 
+(mg)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Vitamin D3 equivalents 
+(µg)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Cobalamin (B12) 
+(ug)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F001236</t>
+          <t>F001234</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Potato, main crop, fresh, raw</t>
+          <t>Broccoli, fresh, raw</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -719,62 +604,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F002001</t>
+          <t>F001235</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apple, fresh, raw, unpeeled</t>
+          <t>Carrot, mature, fresh, raw</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -791,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F002002</t>
+          <t>F001236</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banana, cavendish, fresh, raw</t>
+          <t>Potato, main crop, fresh, raw</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -841,12 +726,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -863,62 +748,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F003001</t>
+          <t>F002001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rice, white, polished, dry</t>
+          <t>Apple, fresh, raw, unpeeled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -935,124 +820,124 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F004001</t>
+          <t>F002002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Milk, cow, fluid, regular fat</t>
+          <t>Banana, cavendish, fresh, raw</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F005001</t>
+          <t>F003001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chicken, breast, lean flesh, baked</t>
+          <t>Rice, white, polished, dry</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1067,154 +952,298 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F001240</t>
+          <t>F004001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spinach, fresh, raw</t>
+          <t>Milk, cow, fluid, regular fat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>F005001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chicken, breast, lean flesh, baked</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F001240</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Spinach, fresh, raw</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>F006001</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Bread, wholemeal, commercial</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>38.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>430</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
